--- a/online_furniture_data_warehousing/docs/data_mapping_final.xlsx
+++ b/online_furniture_data_warehousing/docs/data_mapping_final.xlsx
@@ -42,9 +42,9 @@
   </si>
   <si>
     <t>OrderDate 
--- all distinct order dates
--- as date strings
--- YYYY-MM-DD</t>
+all distinct order dates
+as date strings
+YYYY-MM-DD</t>
   </si>
   <si>
     <t>SCD Type 0 (never overwrite)
@@ -266,7 +266,7 @@
 Reason: Customer relocation
 changes PLZ region -&gt; historical
 orders must stay attributed
-to the old region (Q2 analysis).</t>
+to the old region (for analysis).</t>
   </si>
   <si>
     <t># Stage 1 - RAW_:
@@ -834,7 +834,7 @@
 (no separate dim table)</t>
   </si>
   <si>
-    <t># Stage 2 - FULL_Sales:
+    <t xml:space="preserve"># Stage 2 - FULL_Sales:
   INSERT INTO FULL_BusinessDB_DWH_Sales
   SELECT
     ol.OrderLineId, ol.OrderId,
@@ -858,7 +858,7 @@
 # Stage 3 - FACT_ (Python):
   Resolve SKs from DIM tables
   Read pre-computed measures from FULL_
-  INSERT into FACT_Sales (idempotent)</t>
+  INSERT into FACT_Sales </t>
   </si>
   <si>
     <t>FACT_Sales</t>
@@ -970,7 +970,7 @@
   </si>
   <si>
     <t>~85,500 rows (one per order line)
-Idempotent load: skips already-loaded orders (checked via OrderId).</t>
+skips already-loaded orders (checked via OrderId).</t>
   </si>
   <si>
     <r>
@@ -1396,13 +1396,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>1186713</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>72607</xdr:rowOff>
+      <xdr:rowOff>71972</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>733998</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>332168</xdr:rowOff>
+      <xdr:rowOff>331533</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1484,13 +1484,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>1400810</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>58386</xdr:rowOff>
+      <xdr:rowOff>57751</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>518434</xdr:colOff>
+      <xdr:colOff>518435</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>317948</xdr:rowOff>
+      <xdr:rowOff>317313</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1499,7 +1499,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13249909" y="220311"/>
+          <a:off x="13249910" y="220311"/>
           <a:ext cx="641626" cy="259563"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1756,15 +1756,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1186713</xdr:colOff>
+      <xdr:colOff>1110513</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>234532</xdr:rowOff>
+      <xdr:rowOff>69432</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>733998</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>113093</xdr:rowOff>
+      <xdr:colOff>657798</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>328993</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1773,7 +1773,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1301013" y="234532"/>
+          <a:off x="1224813" y="69432"/>
           <a:ext cx="1223686" cy="259562"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2118,15 +2118,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1186713</xdr:colOff>
+      <xdr:colOff>1196873</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>234532</xdr:rowOff>
+      <xdr:rowOff>107458</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>733998</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>113093</xdr:rowOff>
+      <xdr:colOff>744158</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>367020</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2135,8 +2135,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1301013" y="234532"/>
-          <a:ext cx="1223686" cy="259562"/>
+          <a:off x="1311173" y="107458"/>
+          <a:ext cx="1223686" cy="259563"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3394,7 +3394,7 @@
     <col min="9" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1"/>
+    <row r="1" ht="12.8" customHeight="1"/>
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
